--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1347870-221-CM25</t>
+          <t>1110404-76-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27671.21</v>
+        <v>15586.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1347870-222-CM25</t>
+          <t>1110404-336-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3189.02</v>
+        <v>16992.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2366-4424-CM25</t>
+          <t>1347870-221-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10204.87</v>
+        <v>27671.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>806208-121-CM25</t>
+          <t>1347870-222-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9475.85</v>
+        <v>3189.02</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5952-458-CM25</t>
+          <t>2366-4424-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>16258.04</v>
+        <v>10204.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5420-6-CM26</t>
+          <t>806208-121-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9625.08</v>
+        <v>9475.85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1110404-156-CM26</t>
+          <t>5952-458-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3367.46</v>
+        <v>16258.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1110404-158-CM26</t>
+          <t>5420-6-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10948</v>
+        <v>9625.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5865-36-CM26</t>
+          <t>1110404-156-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11153.87</v>
+        <v>3367.46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1110404-214-CM26</t>
+          <t>1110404-158-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8484.33</v>
+        <v>10948</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>978-50-CM26</t>
+          <t>5865-36-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>12861.88</v>
+        <v>11153.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5512-38-CM26</t>
+          <t>1110404-214-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>16969.88</v>
+        <v>8484.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5512-45-CM26</t>
+          <t>978-50-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>61284.52</v>
+        <v>12861.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1058758-46-CM26</t>
+          <t>5512-38-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>53721.66</v>
+        <v>16969.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1110404-318-CM26</t>
+          <t>5512-45-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>26319.81</v>
+        <v>61284.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5512-58-CM26</t>
+          <t>1058758-46-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3885.35</v>
+        <v>53721.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5512-56-CM26</t>
+          <t>1110404-318-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>330.82</v>
+        <v>26319.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>978-55-CM26</t>
+          <t>5512-58-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>32226.49</v>
+        <v>3885.35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2366-252-CM26</t>
+          <t>5512-56-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,17 +1632,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8211</v>
+        <v>330.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5512-65-CM26</t>
+          <t>978-55-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3718.44</v>
+        <v>32226.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1058758-70-CM26</t>
+          <t>2366-252-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>31396.96</v>
+        <v>8211</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1058758-71-CM26</t>
+          <t>5512-65-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>9234.4</v>
+        <v>3718.44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2366-261-CM26</t>
+          <t>1058758-70-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>25664.73</v>
+        <v>31396.96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1110404-364-CM26</t>
+          <t>1058758-71-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5189.89</v>
+        <v>9234.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5192-11-CM26</t>
+          <t>2366-261-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4843.97</v>
+        <v>25664.73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2366-293-CM26</t>
+          <t>1110404-364-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2998.8</v>
+        <v>5189.89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1317925-46-CM26</t>
+          <t>5192-11-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>792.54</v>
+        <v>4843.97</v>
       </c>
     </row>
     <row r="29">
@@ -2283,7 +2283,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5865-75-CM26</t>
+          <t>2366-293-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,22 +2298,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5140.8</v>
+        <v>2998.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1058758-105-CM26</t>
+          <t>1317925-46-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,22 +2359,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3060.16</v>
+        <v>792.54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2369-28-CM26</t>
+          <t>5865-75-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,32 +2445,28 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>108528.9</v>
+        <v>5140.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5512-80-CM26</t>
+          <t>1058758-105-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2510,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6925.76</v>
+        <v>3060.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5512-81-CM26</t>
+          <t>2369-28-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2546,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2556,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,28 +2567,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6146.21</v>
+        <v>108528.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5512-103-CM26</t>
+          <t>5512-80-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6401.82</v>
+        <v>6925.76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1110404-458-CM26</t>
+          <t>5512-81-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2663,27 +2663,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>11413.29</v>
+        <v>6146.21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1347870-44-CM26</t>
+          <t>5512-103-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2724,27 +2724,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4222.45</v>
+        <v>6401.82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1347870-49-CM26</t>
+          <t>1110404-458-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2170.52</v>
+        <v>11413.29</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1347870-50-CM26</t>
+          <t>1347870-44-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4029.45</v>
+        <v>4222.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1110404-482-CM26</t>
+          <t>1347870-49-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>14441.84</v>
+        <v>2170.52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5512-116-CM26</t>
+          <t>1347870-50-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2973,22 +2973,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>68162.44</v>
+        <v>4029.45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1110404-498-CM26</t>
+          <t>1110404-482-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>706.11</v>
+        <v>14441.84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5865-87-CM26</t>
+          <t>5512-116-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5550.56</v>
+        <v>68162.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1058758-132-CM26</t>
+          <t>1110404-498-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,22 +3156,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2432.34</v>
+        <v>706.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1084148-62-CM26</t>
+          <t>5865-87-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3217,22 +3217,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3517.81</v>
+        <v>5550.56</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1110404-575-CM26</t>
+          <t>1058758-132-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2118.33</v>
+        <v>2432.34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5042-24-CM26</t>
+          <t>1084148-62-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3055.13</v>
+        <v>3517.81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>978-88-CM26</t>
+          <t>1110404-575-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3400,22 +3400,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2579.63</v>
+        <v>2118.33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1110404-583-CM26</t>
+          <t>5042-24-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2824.44</v>
+        <v>3055.13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1110404-614-CM26</t>
+          <t>978-88-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8290.969999999999</v>
+        <v>2579.63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1110404-617-CM26</t>
+          <t>1110404-583-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>419.45</v>
+        <v>2824.44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2366-450-CM26</t>
+          <t>1110404-614-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2234.2</v>
+        <v>8290.969999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2366-451-CM26</t>
+          <t>1110404-617-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3705,22 +3705,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4609.47</v>
+        <v>419.45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2366-423-CM26</t>
+          <t>2366-450-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>12394.8</v>
+        <v>2234.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1110404-708-CM26</t>
+          <t>2366-451-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,22 +3827,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1012.64</v>
+        <v>4609.47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1110404-710-CM26</t>
+          <t>2366-423-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1710.03</v>
+        <v>12394.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1110404-709-CM26</t>
+          <t>1110404-708-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6369.95</v>
+        <v>1012.64</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5864-40-CM26</t>
+          <t>1110404-710-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4010,22 +4010,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2713.91</v>
+        <v>1710.03</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1110404-737-CM26</t>
+          <t>1110404-709-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,6 +4111,128 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
+        <v>6369.95</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>5864-40-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>2713.91</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1110404-737-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
         <v>612.47</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1110404-76-CM25</t>
+          <t>4022-9-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15586.38</v>
+        <v>7860.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1110404-336-CM25</t>
+          <t>1110404-76-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>16992.07</v>
+        <v>15586.38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1347870-221-CM25</t>
+          <t>5512-49-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>27671.21</v>
+        <v>7958.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1347870-222-CM25</t>
+          <t>1260113-1-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3189.02</v>
+        <v>65331.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2366-4424-CM25</t>
+          <t>5512-56-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10204.87</v>
+        <v>11584.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>806208-121-CM25</t>
+          <t>1110404-227-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,43 +874,43 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9475.85</v>
+        <v>20713.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5952-458-CM25</t>
+          <t>5420-90-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,43 +935,43 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16258.04</v>
+        <v>6083.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5420-6-CM26</t>
+          <t>5512-68-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,28 +996,28 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>9625.08</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1110404-156-CM26</t>
+          <t>1084148-40-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3367.46</v>
+        <v>8588.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1110404-158-CM26</t>
+          <t>5951-39-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,43 +1118,43 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10948</v>
+        <v>20677.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5865-36-CM26</t>
+          <t>1151549-103-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11153.87</v>
+        <v>14375.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1110404-214-CM26</t>
+          <t>5512-93-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8484.33</v>
+        <v>12766.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>978-50-CM26</t>
+          <t>1110404-294-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,43 +1301,43 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12861.88</v>
+        <v>9958.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5512-38-CM26</t>
+          <t>1110404-297-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,43 +1362,43 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>16969.88</v>
+        <v>5105.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5512-45-CM26</t>
+          <t>5703-7-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,43 +1423,43 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>61284.52</v>
+        <v>9556.18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1058758-46-CM26</t>
+          <t>1110404-336-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>53721.66</v>
+        <v>16992.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1110404-318-CM26</t>
+          <t>1053139-63-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,43 +1545,43 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>26319.81</v>
+        <v>67472.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5512-58-CM26</t>
+          <t>1110404-378-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,43 +1606,43 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3885.35</v>
+        <v>26068.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5512-56-CM26</t>
+          <t>1110404-451-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,28 +1667,28 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>330.82</v>
+        <v>20122.54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>978-55-CM26</t>
+          <t>5855-141-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,28 +1728,28 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>32226.49</v>
+        <v>10531.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2366-252-CM26</t>
+          <t>1110404-537-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,43 +1789,43 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8211</v>
+        <v>13676.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5512-65-CM26</t>
+          <t>1110404-523-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,43 +1850,43 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3718.44</v>
+        <v>8627.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1058758-70-CM26</t>
+          <t>2366-3957-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,28 +1911,28 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>31396.96</v>
+        <v>17492.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1058758-71-CM26</t>
+          <t>5965-147-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,43 +1972,43 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>9234.4</v>
+        <v>26829.74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2366-261-CM26</t>
+          <t>5952-192-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,43 +2033,43 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>25664.73</v>
+        <v>28742.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1110404-364-CM26</t>
+          <t>5952-191-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,43 +2094,43 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>5189.89</v>
+        <v>21377.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5192-11-CM26</t>
+          <t>1110404-743-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,28 +2155,28 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4843.97</v>
+        <v>4669.35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1317925-47-CM26</t>
+          <t>1110404-764-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,28 +2216,28 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>792.54</v>
+        <v>9133.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1110404-399-CM26</t>
+          <t>1110404-745-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,28 +2277,28 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1349.46</v>
+        <v>10955.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2366-293-CM26</t>
+          <t>1110404-815-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,28 +2338,28 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2998.8</v>
+        <v>6294.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1317925-46-CM26</t>
+          <t>1110404-891-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,28 +2399,28 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>792.54</v>
+        <v>8958.92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5865-75-CM26</t>
+          <t>5865-87-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,43 +2460,43 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5140.8</v>
+        <v>15972.78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1058758-105-CM26</t>
+          <t>1110404-995-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,43 +2521,43 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3060.16</v>
+        <v>18293.28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2369-28-CM26</t>
+          <t>1110404-998-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,62 +2567,58 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>108528.9</v>
+        <v>6571.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5512-80-CM26</t>
+          <t>1347870-98-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2632,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2647,43 +2643,43 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6925.76</v>
+        <v>3071.63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5512-81-CM26</t>
+          <t>1347870-96-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2708,43 +2704,43 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6146.21</v>
+        <v>5515.54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5512-103-CM26</t>
+          <t>1347870-97-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,43 +2765,43 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>6401.82</v>
+        <v>5697.72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1110404-458-CM26</t>
+          <t>5512-213-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,28 +2826,28 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>11413.29</v>
+        <v>8508.379999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1347870-44-CM26</t>
+          <t>1110404-1031-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2861,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,28 +2887,28 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4222.45</v>
+        <v>70199.34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1347870-49-CM26</t>
+          <t>1110404-1054-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2922,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,43 +2948,43 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2170.52</v>
+        <v>8043.15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1347870-50-CM26</t>
+          <t>5864-32-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3013,28 +3009,28 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4029.45</v>
+        <v>8682.299999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1110404-482-CM26</t>
+          <t>1110404-1059-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3059,7 +3055,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3074,43 +3070,43 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>14441.84</v>
+        <v>6222.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5512-116-CM26</t>
+          <t>2366-4163-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3120,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3135,43 +3131,43 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>68162.44</v>
+        <v>4045.58</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1110404-498-CM26</t>
+          <t>5864-34-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3181,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3196,43 +3192,43 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>706.11</v>
+        <v>10967.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5865-87-CM26</t>
+          <t>1110404-1048-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3242,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3257,43 +3253,43 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5550.56</v>
+        <v>70314.36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1058758-132-CM26</t>
+          <t>1110404-1129-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3303,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3318,43 +3314,43 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2432.34</v>
+        <v>12411.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1084148-62-CM26</t>
+          <t>5965-236-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3379,28 +3375,28 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3517.81</v>
+        <v>32569.11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1110404-575-CM26</t>
+          <t>1084148-119-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3440,28 +3436,28 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2118.33</v>
+        <v>2979.64</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5042-24-CM26</t>
+          <t>1110404-1263-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3471,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,28 +3497,28 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3055.13</v>
+        <v>5272.81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>978-88-CM26</t>
+          <t>1058758-262-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3532,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3547,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3562,28 +3558,28 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2579.63</v>
+        <v>30196.25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1110404-583-CM26</t>
+          <t>1347870-146-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3593,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3608,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,43 +3619,43 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2824.44</v>
+        <v>6409.04</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1110404-614-CM26</t>
+          <t>1347870-145-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3669,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3684,28 +3680,28 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8290.969999999999</v>
+        <v>20835.71</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1110404-617-CM26</t>
+          <t>2585-4257-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3715,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3745,43 +3741,43 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>419.45</v>
+        <v>22399.97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2366-450-CM26</t>
+          <t>1110404-1308-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3806,28 +3802,28 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2234.2</v>
+        <v>19263.72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2366-451-CM26</t>
+          <t>806208-77-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,43 +3863,43 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4609.47</v>
+        <v>5873.84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2366-423-CM26</t>
+          <t>1110404-1375-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,28 +3924,28 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>12394.8</v>
+        <v>32115.72</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1110404-708-CM26</t>
+          <t>1110404-1376-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3974,7 +3970,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3989,28 +3985,28 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1012.64</v>
+        <v>68172.72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1110404-710-CM26</t>
+          <t>1110404-1377-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4035,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,43 +4046,43 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1710.03</v>
+        <v>70233.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1110404-709-CM26</t>
+          <t>5951-186-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,43 +4107,43 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6369.95</v>
+        <v>14788.37</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5864-40-CM26</t>
+          <t>5420-288-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4157,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4172,43 +4168,43 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2713.91</v>
+        <v>12696.42</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1110404-737-CM26</t>
+          <t>1347870-221-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,7 +4229,4285 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
+        <v>27671.21</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1347870-222-CM25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>3189.02</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2366-4424-CM25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>10204.87</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>806208-121-CM25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>9475.85</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>5952-458-CM25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>COMPUNOW SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>78.218.816-K</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>16258.04</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>5420-6-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.978.890-7</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>COMPUNOW SPA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>78.218.816-K</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>9625.08</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1110404-156-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>3367.46</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1110404-158-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>10948</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>5865-36-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>11153.87</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1110404-214-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>8484.33</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>978-50-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>RyC Servicios Computacionales Ltda</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>12861.88</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>5512-38-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>16969.88</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>5512-45-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>61284.52</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1058758-46-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>77.137.827-7</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>53721.66</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1110404-318-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>26319.81</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>5512-58-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>3885.35</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1058758-70-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>31396.96</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>5512-65-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>3718.44</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1058758-71-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>9234.4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>978-55-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>32226.49</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>5512-56-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>330.82</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2366-252-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>8211</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2366-261-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>25664.73</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1110404-364-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>5189.89</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>5192-11-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>4843.97</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1110404-399-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>1349.46</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1317925-47-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>792.54</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2366-293-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>2998.8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1317925-46-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>792.54</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>5865-75-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>5140.8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1058758-105-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>3060.16</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2369-28-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>108528.9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>5512-80-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>SANDOS SPA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>6925.76</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>5512-81-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>6146.21</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>5512-103-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>6401.82</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1110404-458-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>SANDOS SPA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>11413.29</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1110404-482-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>14441.84</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1347870-50-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>4029.45</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1347870-49-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>2170.52</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1347870-44-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>RyC Servicios Computacionales Ltda</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>4222.45</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>5512-116-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>SANDOS SPA</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>68162.44</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1110404-498-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>706.11</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>5865-87-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>5550.56</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1058758-132-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>2432.34</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1084148-62-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>3517.81</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1110404-575-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>2118.33</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>5042-24-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>77.727.285-3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>3055.13</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>978-88-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>2579.63</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1110404-583-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>2824.44</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1110404-614-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>8290.969999999999</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1110404-617-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>419.45</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2366-450-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>2234.2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2366-451-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>4609.47</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2366-423-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>12394.8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1110404-710-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>1710.03</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1110404-708-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>1012.64</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1110404-709-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>6369.95</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>5864-40-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>2713.91</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1110404-737-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
         <v>612.47</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1053139-120-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>I.I.A. Ltda.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>7556.48</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1110404-785-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>3986.5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1053139-125-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Clevertec</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>628.03</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1053139-129-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>77.727.285-3</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>995.64</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2369-75-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>289777.42</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1110404-806-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>15721.74</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1110404-822-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>4287.75</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1110404-824-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>5555.61</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>5512-194-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>3962.7</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1110404-835-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>2373.01</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1110404-847-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>17150.99</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>5951-106-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>18378.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M132"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5420-90-CM25</t>
+          <t>5512-68-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6083.28</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5512-68-CM25</t>
+          <t>5420-90-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,17 +961,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2733</v>
+        <v>6083.28</v>
       </c>
     </row>
     <row r="10">
@@ -2588,7 +2588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1347870-98-CM25</t>
+          <t>1347870-96-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3071.63</v>
+        <v>5515.54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1347870-96-CM25</t>
+          <t>1347870-98-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5515.54</v>
+        <v>3071.63</v>
       </c>
     </row>
     <row r="38">
@@ -2893,7 +2893,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1110404-1054-CM25</t>
+          <t>5864-32-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8043.15</v>
+        <v>8682.299999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5864-32-CM25</t>
+          <t>1110404-1054-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>8682.299999999999</v>
+        <v>8043.15</v>
       </c>
     </row>
     <row r="43">
@@ -3076,7 +3076,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2366-4163-CM25</t>
+          <t>5864-34-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3096,17 +3096,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4045.58</v>
+        <v>10967.28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5864-34-CM25</t>
+          <t>1110404-1048-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3157,17 +3157,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10967.28</v>
+        <v>70314.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1110404-1048-CM25</t>
+          <t>2366-4163-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>70314.36</v>
+        <v>4045.58</v>
       </c>
     </row>
     <row r="47">
@@ -3564,7 +3564,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1347870-146-CM25</t>
+          <t>1347870-145-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>6409.04</v>
+        <v>20835.71</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1347870-145-CM25</t>
+          <t>1347870-146-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>20835.71</v>
+        <v>6409.04</v>
       </c>
     </row>
     <row r="54">
@@ -3747,7 +3747,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1110404-1308-CM25</t>
+          <t>806208-77-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3767,17 +3767,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>19263.72</v>
+        <v>5873.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>806208-77-CM25</t>
+          <t>1110404-1308-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>5873.84</v>
+        <v>19263.72</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1110404-1375-CM25</t>
+          <t>1110404-1377-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>32115.72</v>
+        <v>70233.8</v>
       </c>
     </row>
     <row r="58">
@@ -3991,7 +3991,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1110404-1377-CM25</t>
+          <t>1110404-1375-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>70233.8</v>
+        <v>32115.72</v>
       </c>
     </row>
     <row r="60">
@@ -4174,7 +4174,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1347870-221-CM25</t>
+          <t>1347870-222-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>27671.21</v>
+        <v>3189.02</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1347870-222-CM25</t>
+          <t>1347870-221-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3189.02</v>
+        <v>27671.21</v>
       </c>
     </row>
     <row r="64">
@@ -4479,7 +4479,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5420-6-CM26</t>
+          <t>1053139-4-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,27 +4489,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>9625.08</v>
+        <v>3936.42</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1110404-156-CM26</t>
+          <t>5420-6-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3367.46</v>
+        <v>9625.08</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1110404-158-CM26</t>
+          <t>1110404-156-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>10948</v>
+        <v>3367.46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5865-36-CM26</t>
+          <t>1110404-158-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,22 +4677,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>11153.87</v>
+        <v>10948</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1110404-214-CM26</t>
+          <t>5865-36-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8484.33</v>
+        <v>11153.87</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>978-50-CM26</t>
+          <t>1110404-214-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>12861.88</v>
+        <v>8484.33</v>
       </c>
     </row>
     <row r="73">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5150,7 +5150,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1058758-70-CM26</t>
+          <t>1058758-71-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>31396.96</v>
+        <v>9234.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5512-65-CM26</t>
+          <t>1058758-70-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3718.44</v>
+        <v>31396.96</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1058758-71-CM26</t>
+          <t>5512-56-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>9234.4</v>
+        <v>330.82</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>978-55-CM26</t>
+          <t>2366-252-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>32226.49</v>
+        <v>8211</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5512-56-CM26</t>
+          <t>5512-65-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>330.82</v>
+        <v>3718.44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2366-252-CM26</t>
+          <t>2366-261-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>8211</v>
+        <v>25664.73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2366-261-CM26</t>
+          <t>1110404-364-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>25664.73</v>
+        <v>5189.89</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1110404-364-CM26</t>
+          <t>5192-11-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,27 +5587,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5189.89</v>
+        <v>4843.97</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5192-11-CM26</t>
+          <t>1110404-399-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,22 +5653,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4843.97</v>
+        <v>1349.46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1110404-399-CM26</t>
+          <t>1317925-47-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1349.46</v>
+        <v>792.54</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1317925-47-CM26</t>
+          <t>2366-293-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>792.54</v>
+        <v>2998.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2366-293-CM26</t>
+          <t>1317925-46-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2998.8</v>
+        <v>792.54</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1317925-46-CM26</t>
+          <t>5865-75-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,22 +5897,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>792.54</v>
+        <v>5140.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5865-75-CM26</t>
+          <t>1058758-105-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>5140.8</v>
+        <v>3060.16</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1058758-105-CM26</t>
+          <t>2369-28-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,28 +6044,32 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3060.16</v>
+        <v>108528.9</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2369-28-CM26</t>
+          <t>5512-80-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6084,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6094,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,32 +6109,28 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>108528.9</v>
+        <v>6925.76</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5512-80-CM26</t>
+          <t>5512-81-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>6925.76</v>
+        <v>6146.21</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5512-81-CM26</t>
+          <t>5512-103-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>6146.21</v>
+        <v>6401.82</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5512-103-CM26</t>
+          <t>1110404-458-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6262,27 +6262,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>6401.82</v>
+        <v>11413.29</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1110404-458-CM26</t>
+          <t>1347870-44-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6368,13 +6368,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>11413.29</v>
+        <v>4222.45</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1110404-482-CM26</t>
+          <t>1347870-49-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>14441.84</v>
+        <v>2170.52</v>
       </c>
     </row>
     <row r="99">
@@ -6496,7 +6496,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1347870-49-CM26</t>
+          <t>1110404-482-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2170.52</v>
+        <v>14441.84</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1347870-44-CM26</t>
+          <t>5512-116-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6572,22 +6572,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4222.45</v>
+        <v>68162.44</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5512-116-CM26</t>
+          <t>1110404-498-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6638,17 +6638,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>68162.44</v>
+        <v>706.11</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1110404-498-CM26</t>
+          <t>5865-87-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6694,22 +6694,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>706.11</v>
+        <v>5550.56</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5865-87-CM26</t>
+          <t>1058758-132-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>5550.56</v>
+        <v>2432.34</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1058758-132-CM26</t>
+          <t>1084148-62-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6816,22 +6816,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2432.34</v>
+        <v>3517.81</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1084148-62-CM26</t>
+          <t>1110404-575-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3517.81</v>
+        <v>2118.33</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1110404-575-CM26</t>
+          <t>5042-24-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2118.33</v>
+        <v>3055.13</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5042-24-CM26</t>
+          <t>1110404-583-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3055.13</v>
+        <v>2824.44</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>978-88-CM26</t>
+          <t>1053139-91-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2579.63</v>
+        <v>963.9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1110404-583-CM26</t>
+          <t>1110404-614-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2824.44</v>
+        <v>8290.969999999999</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1110404-614-CM26</t>
+          <t>1110404-617-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>8290.969999999999</v>
+        <v>419.45</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1110404-617-CM26</t>
+          <t>2366-450-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7243,22 +7243,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>419.45</v>
+        <v>2234.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2366-450-CM26</t>
+          <t>2366-451-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7329,12 +7329,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2234.2</v>
+        <v>4609.47</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2366-451-CM26</t>
+          <t>2366-423-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>4609.47</v>
+        <v>12394.8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2366-423-CM26</t>
+          <t>1110404-708-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7426,22 +7426,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>12394.8</v>
+        <v>1012.64</v>
       </c>
     </row>
     <row r="116">
@@ -7533,7 +7533,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1110404-708-CM26</t>
+          <t>1110404-709-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1012.64</v>
+        <v>6369.95</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1110404-709-CM26</t>
+          <t>5864-40-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7614,17 +7614,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>6369.95</v>
+        <v>2713.91</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5864-40-CM26</t>
+          <t>1110404-737-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7670,22 +7670,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2713.91</v>
+        <v>612.47</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1110404-737-CM26</t>
+          <t>1053139-120-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>612.47</v>
+        <v>7556.48</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1053139-120-CM26</t>
+          <t>1110404-785-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7792,22 +7792,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7817,12 +7817,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>7556.48</v>
+        <v>3986.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1110404-785-CM26</t>
+          <t>1053139-125-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7858,17 +7858,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3986.5</v>
+        <v>628.03</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1053139-125-CM26</t>
+          <t>1053139-129-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7954,13 +7954,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>628.03</v>
+        <v>995.64</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1053139-129-CM26</t>
+          <t>2369-75-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7975,22 +7975,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8000,28 +8000,32 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>995.64</v>
+        <v>289777.42</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2369-75-CM26</t>
+          <t>1110404-806-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8041,17 +8045,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8061,32 +8065,28 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>289777.42</v>
+        <v>15721.74</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1110404-806-CM26</t>
+          <t>1110404-822-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8141,13 +8141,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>15721.74</v>
+        <v>4287.75</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1110404-822-CM26</t>
+          <t>1110404-824-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8202,13 +8202,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>4287.75</v>
+        <v>5555.61</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1110404-824-CM26</t>
+          <t>1110404-835-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5555.61</v>
+        <v>2373.01</v>
       </c>
     </row>
     <row r="129">
@@ -8330,7 +8330,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1110404-835-CM26</t>
+          <t>1110404-847-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8385,13 +8385,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2373.01</v>
+        <v>17150.99</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1110404-847-CM26</t>
+          <t>5951-106-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8406,22 +8406,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8446,13 +8446,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>17150.99</v>
+        <v>18378.36</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5951-106-CM26</t>
+          <t>5473-133-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.978.970-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8507,7 +8507,312 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>18378.36</v>
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1110404-910-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>4133.63</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1110404-911-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>18278.4</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1053139-140-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>2424.03</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1707-38-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>60.511.139-4</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1053139-145-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>1915.78</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
@@ -623,7 +623,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1716,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1842,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1907,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1972,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2037,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2102,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2228,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2293,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2358,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2423,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2488,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2553,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2618,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2683,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2809,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2874,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2939,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3004,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3069,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3134,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3199,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3325,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3390,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3455,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3520,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3585,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3650,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3715,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3841,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3906,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4032,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4097,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4162,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4227,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4292,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4357,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4422,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4487,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4552,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4617,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4682,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4747,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4812,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4877,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4942,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5007,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5072,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5137,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5202,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5267,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5332,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5580,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5645,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5710,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5836,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5901,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5966,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6031,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6096,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6161,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6226,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6291,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6421,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6486,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6551,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6616,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6742,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6807,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6872,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6937,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +7002,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7189,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7254,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7319,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7384,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7449,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7514,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7579,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7644,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7770,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7835,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7961,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8026,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8091,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8217,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8343,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8473,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8538,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8195,7 +8603,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8668,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8378,7 +8794,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8859,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8500,7 +8924,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8561,7 +8989,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8622,7 +9054,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8744,7 +9180,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8805,7 +9245,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5512-68-CM25</t>
+          <t>5420-90-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -912,17 +912,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2733</v>
+        <v>6083.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5420-90-CM25</t>
+          <t>5512-68-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6083.28</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="10">
@@ -2245,7 +2245,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1110404-764-CM25</t>
+          <t>1110404-745-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9133.49</v>
+        <v>10955.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1110404-745-CM25</t>
+          <t>1110404-764-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10955.5</v>
+        <v>9133.49</v>
       </c>
     </row>
     <row r="31">
@@ -2761,7 +2761,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1347870-98-CM25</t>
+          <t>1347870-97-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2820,13 +2820,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3071.63</v>
+        <v>5697.72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1347870-97-CM25</t>
+          <t>1347870-98-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5697.72</v>
+        <v>3071.63</v>
       </c>
     </row>
     <row r="39">
@@ -3021,7 +3021,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5864-32-CM25</t>
+          <t>1110404-1054-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8682.299999999999</v>
+        <v>8043.15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1110404-1054-CM25</t>
+          <t>5864-32-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3106,17 +3106,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>8043.15</v>
+        <v>8682.299999999999</v>
       </c>
     </row>
     <row r="43">
@@ -3216,7 +3216,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5864-34-CM25</t>
+          <t>2366-4163-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3236,17 +3236,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3256,28 +3256,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>10967.28</v>
+        <v>4045.58</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1110404-1048-CM25</t>
+          <t>5864-34-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3297,17 +3301,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3317,32 +3321,28 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>70314.36</v>
+        <v>10967.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2366-4163-CM25</t>
+          <t>1110404-1048-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4045.58</v>
+        <v>70314.36</v>
       </c>
     </row>
     <row r="47">
@@ -3732,7 +3732,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1347870-145-CM25</t>
+          <t>1347870-146-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3772,28 +3772,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>20835.71</v>
+        <v>6409.04</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1347870-146-CM25</t>
+          <t>1347870-145-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3833,32 +3837,28 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>6409.04</v>
+        <v>20835.71</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2585-4257-CM25</t>
+          <t>806208-77-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3878,17 +3878,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3898,32 +3898,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>22399.97</v>
+        <v>5873.84</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>806208-77-CM25</t>
+          <t>1110404-1308-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3943,17 +3939,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3963,28 +3959,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5873.84</v>
+        <v>19263.72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1110404-1308-CM25</t>
+          <t>2585-4257-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>19263.72</v>
+        <v>22399.97</v>
       </c>
     </row>
     <row r="57">
@@ -5532,7 +5532,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5512-56-CM26</t>
+          <t>5512-65-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>330.82</v>
+        <v>3718.44</v>
       </c>
     </row>
     <row r="81">
@@ -5662,7 +5662,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5512-65-CM26</t>
+          <t>5512-56-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3718.44</v>
+        <v>330.82</v>
       </c>
     </row>
     <row r="83">
@@ -5983,7 +5983,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1317925-47-CM26</t>
+          <t>1317925-46-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6113,7 +6113,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1317925-46-CM26</t>
+          <t>1317925-47-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6373,7 +6373,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5512-80-CM26</t>
+          <t>5512-81-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6432,13 +6432,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>6925.76</v>
+        <v>6146.21</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5512-81-CM26</t>
+          <t>5512-80-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>6146.21</v>
+        <v>6925.76</v>
       </c>
     </row>
     <row r="95">
@@ -6633,7 +6633,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1347870-44-CM26</t>
+          <t>1110404-482-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6673,22 +6673,26 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4222.45</v>
+        <v>14441.84</v>
       </c>
     </row>
     <row r="98">
@@ -6759,7 +6763,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1347870-50-CM26</t>
+          <t>1347870-44-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6799,32 +6803,28 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4029.45</v>
+        <v>4222.45</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1110404-482-CM26</t>
+          <t>1347870-50-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6883,13 +6883,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>14441.84</v>
+        <v>4029.45</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5512-116-CM26</t>
+          <t>1110404-498-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6909,17 +6909,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6948,13 +6948,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>68162.44</v>
+        <v>706.11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1110404-498-CM26</t>
+          <t>5512-116-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6974,17 +6974,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6994,12 +6994,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>706.11</v>
+        <v>68162.44</v>
       </c>
     </row>
     <row r="103">
@@ -7787,7 +7787,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1110404-708-CM26</t>
+          <t>1110404-710-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7827,32 +7827,28 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1012.64</v>
+        <v>1710.03</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1110404-710-CM26</t>
+          <t>1110404-708-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7892,28 +7888,32 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1710.03</v>
+        <v>1012.64</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1110404-709-CM26</t>
+          <t>5864-40-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7933,17 +7933,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7953,17 +7953,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7972,13 +7972,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6369.95</v>
+        <v>2713.91</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5864-40-CM26</t>
+          <t>1110404-709-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7998,17 +7998,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8018,17 +8018,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2713.91</v>
+        <v>6369.95</v>
       </c>
     </row>
     <row r="119">
@@ -8169,7 +8169,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1110404-785-CM26</t>
+          <t>1053139-129-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8189,17 +8189,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3986.5</v>
+        <v>995.64</v>
       </c>
     </row>
     <row r="122">
@@ -8295,7 +8295,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1053139-129-CM26</t>
+          <t>1110404-785-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8354,13 +8354,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>995.64</v>
+        <v>3986.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2369-75-CM26</t>
+          <t>1110404-806-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8419,13 +8419,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>289777.42</v>
+        <v>15721.74</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1110404-806-CM26</t>
+          <t>2369-75-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>15721.74</v>
+        <v>289777.42</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1110404-822-CM26</t>
+          <t>1110404-824-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8549,13 +8549,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4287.75</v>
+        <v>5555.61</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1110404-824-CM26</t>
+          <t>1110404-822-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8614,13 +8614,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>5555.61</v>
+        <v>4287.75</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1110404-835-CM26</t>
+          <t>5512-194-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8640,17 +8640,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8660,32 +8660,28 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2373.01</v>
+        <v>3962.7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5512-194-CM26</t>
+          <t>1110404-835-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8705,17 +8701,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8725,22 +8721,26 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3962.7</v>
+        <v>2373.01</v>
       </c>
     </row>
     <row r="130">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -9257,6 +9257,701 @@
       </c>
       <c r="M137" s="2" t="n">
         <v>1915.78</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>5952-165-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>10810.48</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1058758-289-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>2260.98</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>553368-155-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>4517.24</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>5952-168-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>7476.18</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1053139-170-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>57596</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1110404-1007-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>4022.15</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1110404-1000-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>1479.17</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1110404-1023-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>1206.66</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>941739-99-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>70.770.800-K</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>4788.54</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>5512-237-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>I.I.A. Ltda.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>2927.4</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>5358-316-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>SANDOS SPA</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>4259.01</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
@@ -7616,7 +7616,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1794,7 +1794,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1110404-537-CM25</t>
+          <t>1110404-523-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13676.08</v>
+        <v>8627.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1110404-523-CM25</t>
+          <t>1110404-537-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8627.5</v>
+        <v>13676.08</v>
       </c>
     </row>
     <row r="24">
@@ -2054,7 +2054,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5952-192-CM25</t>
+          <t>5952-191-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2094,32 +2094,28 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>28742.38</v>
+        <v>21377.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5952-191-CM25</t>
+          <t>5952-192-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2159,22 +2155,26 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>21377.16</v>
+        <v>28742.38</v>
       </c>
     </row>
     <row r="28">
@@ -3858,7 +3858,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>806208-77-CM25</t>
+          <t>2585-4257-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3878,17 +3878,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3898,28 +3898,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>5873.84</v>
+        <v>22399.97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1110404-1308-CM25</t>
+          <t>806208-77-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3939,17 +3943,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3959,32 +3963,28 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>19263.72</v>
+        <v>5873.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2585-4257-CM25</t>
+          <t>1110404-1308-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>22399.97</v>
+        <v>19263.72</v>
       </c>
     </row>
     <row r="57">
@@ -5983,7 +5983,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1317925-46-CM26</t>
+          <t>1317925-47-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6048,7 +6048,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2366-293-CM26</t>
+          <t>1317925-46-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6107,13 +6107,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2998.8</v>
+        <v>792.54</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1317925-47-CM26</t>
+          <t>2366-293-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>792.54</v>
+        <v>2998.8</v>
       </c>
     </row>
     <row r="90">
@@ -6698,7 +6698,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1347870-49-CM26</t>
+          <t>1347870-50-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2170.52</v>
+        <v>4029.45</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1347870-44-CM26</t>
+          <t>1347870-49-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6803,28 +6803,32 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4222.45</v>
+        <v>2170.52</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1347870-50-CM26</t>
+          <t>1347870-44-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6864,26 +6868,22 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4029.45</v>
+        <v>4222.45</v>
       </c>
     </row>
     <row r="101">
@@ -7787,7 +7787,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1110404-710-CM26</t>
+          <t>1110404-708-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7827,28 +7827,32 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1710.03</v>
+        <v>1012.64</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1110404-708-CM26</t>
+          <t>1110404-710-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7888,26 +7892,22 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1012.64</v>
+        <v>1710.03</v>
       </c>
     </row>
     <row r="117">
@@ -8169,7 +8169,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1053139-129-CM26</t>
+          <t>1110404-785-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8189,17 +8189,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8228,13 +8228,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>995.64</v>
+        <v>3986.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1053139-125-CM26</t>
+          <t>1053139-129-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8274,28 +8274,32 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+          <t>77.727.285-3</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>628.03</v>
+        <v>995.64</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1110404-785-CM26</t>
+          <t>1053139-125-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8315,17 +8319,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8335,26 +8339,22 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3986.5</v>
+        <v>628.03</v>
       </c>
     </row>
     <row r="124">
@@ -8490,7 +8490,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1110404-824-CM26</t>
+          <t>1110404-822-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8549,13 +8549,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>5555.61</v>
+        <v>4287.75</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1110404-822-CM26</t>
+          <t>1110404-824-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>4287.75</v>
+        <v>5555.61</v>
       </c>
     </row>
     <row r="128">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9705,7 +9705,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1110404-1023-CM26</t>
+          <t>941739-99-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9745,32 +9745,28 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1206.66</v>
+        <v>4788.54</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>941739-99-CM26</t>
+          <t>1110404-1023-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9795,12 +9791,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9810,28 +9806,32 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>4788.54</v>
+        <v>1206.66</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5512-237-CM26</t>
+          <t>5358-316-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9871,28 +9871,32 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
+          <t>77.319.537-4</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2927.4</v>
+        <v>4259.01</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5358-316-CM26</t>
+          <t>5512-237-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9932,26 +9936,152 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4259.01</v>
+        <v>2927.4</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1194619-57-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>2260.93</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1110404-1041-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>1639.34</v>
       </c>
     </row>
   </sheetData>
